--- a/output/勤務表_2026年1月.xlsx
+++ b/output/勤務表_2026年1月.xlsx
@@ -978,42 +978,38 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr">
         <is>
@@ -1023,47 +1019,51 @@
       <c r="V4" s="5" t="inlineStr"/>
       <c r="W4" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="X4" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr"/>
-      <c r="AB4" s="5" t="inlineStr"/>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr"/>
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="AE4" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AF4" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AF4" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AG4" s="5" t="inlineStr"/>
+      <c r="AG4" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="AH4" s="5" t="n">
         <v>0</v>
       </c>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AM4" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN4" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO4" s="5" t="n">
         <v>0</v>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>夜</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
+      <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>CT</t>
@@ -1144,99 +1144,95 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>病院MR</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr"/>
+      <c r="AB5" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="X5" s="5" t="inlineStr">
+      <c r="AC5" s="5" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="Y5" s="5" t="inlineStr"/>
-      <c r="Z5" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="AA5" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="AB5" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC5" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="AD5" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>病院MR</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -1255,7 +1251,7 @@
         </is>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI5" s="5" t="n">
         <v>0</v>
@@ -1273,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="AN5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO5" s="5" t="n">
         <v>0</v>
@@ -1282,22 +1278,22 @@
         <v>0</v>
       </c>
       <c r="AQ5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="AR5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1447,52 +1443,40 @@
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr"/>
@@ -1502,16 +1486,8 @@
           <t>病院MR</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
       <c r="X7" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
@@ -1539,13 +1515,17 @@
           <t>クMR</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr"/>
-      <c r="AG7" s="5" t="inlineStr"/>
+      <c r="AG7" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
       <c r="AH7" s="5" t="n">
         <v>0</v>
       </c>
@@ -1692,11 +1672,7 @@
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
+      <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
@@ -1710,7 +1686,7 @@
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>病院MR</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr"/>
@@ -1730,36 +1706,32 @@
           <t>病院MR</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
+      <c r="R9" s="5" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr"/>
       <c r="U9" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="X9" s="5" t="inlineStr">
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
-        </is>
-      </c>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
         </is>
       </c>
       <c r="Z9" s="5" t="inlineStr"/>
@@ -1779,12 +1751,12 @@
           <t>クMR</t>
         </is>
       </c>
-      <c r="AE9" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="AF9" s="5" t="inlineStr"/>
+      <c r="AE9" s="5" t="inlineStr"/>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
       <c r="AG9" s="9" t="inlineStr">
         <is>
           <t>☆</t>
@@ -1849,41 +1821,41 @@
       <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
+      <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr"/>
       <c r="O10" s="5" t="inlineStr">
         <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
@@ -1920,7 +1892,11 @@
           <t>クMR</t>
         </is>
       </c>
-      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
       <c r="AA10" s="5" t="inlineStr"/>
       <c r="AB10" s="5" t="inlineStr">
         <is>
@@ -1932,22 +1908,22 @@
           <t>病院MR</t>
         </is>
       </c>
-      <c r="AD10" s="5" t="inlineStr"/>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
       <c r="AE10" s="5" t="inlineStr">
         <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="AF10" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="AF10" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="AG10" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
+      <c r="AG10" s="5" t="inlineStr"/>
       <c r="AH10" s="5" t="n">
         <v>0</v>
       </c>
@@ -2008,105 +1984,101 @@
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="P11" s="5" t="inlineStr">
         <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr"/>
       <c r="U11" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="V11" s="5" t="inlineStr"/>
-      <c r="W11" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="X11" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Y11" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="AA11" s="5" t="inlineStr"/>
       <c r="AB11" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AC11" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AD11" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="AE11" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AF11" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
-        </is>
-      </c>
-      <c r="AF11" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
         </is>
       </c>
       <c r="AG11" s="5" t="inlineStr">
@@ -2124,16 +2096,16 @@
         <v>2</v>
       </c>
       <c r="AK11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="AL11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="AO11" s="5" t="n">
         <v>0</v>
@@ -2189,29 +2161,29 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ア</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr"/>
       <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="P12" s="5" t="inlineStr">
@@ -2221,72 +2193,68 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>心夜</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
+      <c r="X12" s="5" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="W12" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="X12" s="5" t="inlineStr">
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AA12" s="5" t="inlineStr"/>
+      <c r="AB12" s="5" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>CT夜</t>
-        </is>
-      </c>
-      <c r="AA12" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AB12" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="AC12" s="5" t="inlineStr">
         <is>
-          <t>心</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AD12" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>ア</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2296,34 +2264,34 @@
       </c>
       <c r="AF12" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ア</t>
         </is>
       </c>
       <c r="AG12" s="6" t="inlineStr">
         <is>
-          <t>CT夜(希)</t>
+          <t>心夜(希)</t>
         </is>
       </c>
       <c r="AH12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN12" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="AI12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN12" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="AO12" s="5" t="n">
         <v>0</v>
@@ -2344,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="AU12" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV12" s="5" t="n">
         <v>0</v>
@@ -2363,34 +2331,26 @@
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr"/>
@@ -2402,17 +2362,17 @@
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>心</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
           <t>HB</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
@@ -2423,65 +2383,65 @@
       <c r="T13" s="5" t="inlineStr"/>
       <c r="U13" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
       <c r="W13" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="X13" s="5" t="inlineStr">
+        <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="X13" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="Y13" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
-        </is>
-      </c>
-      <c r="Z13" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
         </is>
       </c>
       <c r="AA13" s="5" t="inlineStr"/>
       <c r="AB13" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>心</t>
         </is>
       </c>
       <c r="AC13" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AD13" s="5" t="inlineStr">
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="AE13" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AF13" s="5" t="inlineStr">
+      <c r="AG13" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AG13" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="AH13" s="5" t="n">
         <v>0</v>
       </c>
@@ -2498,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN13" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AO13" s="5" t="n">
         <v>0</v>
@@ -2513,13 +2473,13 @@
         <v>0</v>
       </c>
       <c r="AR13" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AT13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" s="5" t="n">
         <v>0</v>
@@ -2543,32 +2503,28 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr"/>
@@ -2578,19 +2534,15 @@
           <t>DR</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
+      <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr"/>
@@ -2602,23 +2554,27 @@
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="X14" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr"/>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="AA14" s="5" t="inlineStr"/>
@@ -2629,29 +2585,25 @@
       </c>
       <c r="AC14" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="AD14" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AE14" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
       <c r="AF14" s="5" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="AG14" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
+      <c r="AG14" s="5" t="inlineStr"/>
       <c r="AH14" s="5" t="n">
         <v>0</v>
       </c>
@@ -2671,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO14" s="5" t="n">
         <v>0</v>
@@ -2695,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="AV14" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -2724,24 +2676,20 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -2761,49 +2709,45 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
         <is>
           <t>精</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
       <c r="X15" s="5" t="inlineStr">
         <is>
-          <t>心</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="Y15" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="Z15" s="5" t="inlineStr">
@@ -2814,27 +2758,27 @@
       <c r="AA15" s="5" t="inlineStr"/>
       <c r="AB15" s="5" t="inlineStr">
         <is>
-          <t>心</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="AC15" s="5" t="inlineStr">
         <is>
-          <t>ク/17休</t>
+          <t>CT/17休</t>
         </is>
       </c>
       <c r="AD15" s="5" t="inlineStr">
         <is>
-          <t>CT/17休</t>
+          <t>精/17休</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="AF15" s="6" t="inlineStr">
         <is>
-          <t>精夜(希)</t>
+          <t>病CT夜(希)</t>
         </is>
       </c>
       <c r="AG15" s="7" t="inlineStr">
@@ -2852,40 +2796,40 @@
         <v>0</v>
       </c>
       <c r="AK15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AL15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="5" t="n">
+      <c r="AN15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="AN15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2914,106 +2858,106 @@
           <t>休</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="inlineStr">
         <is>
           <t>精</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="Z16" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="Z16" s="5" t="inlineStr"/>
       <c r="AA16" s="5" t="inlineStr"/>
       <c r="AB16" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>病院MR</t>
         </is>
       </c>
       <c r="AC16" s="6" t="inlineStr">
         <is>
-          <t>DR夜(希)</t>
+          <t>クMR夜(希)</t>
         </is>
       </c>
       <c r="AD16" s="7" t="inlineStr">
@@ -3028,7 +2972,7 @@
       </c>
       <c r="AF16" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>精</t>
         </is>
       </c>
       <c r="AG16" s="5" t="inlineStr">
@@ -3046,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="5" t="n">
         <v>0</v>
@@ -3055,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO16" s="5" t="n">
         <v>0</v>
@@ -3064,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="AQ16" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AR16" s="5" t="n">
         <v>0</v>
@@ -3079,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AV16" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3111,16 +3055,20 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
           <t>夜</t>
@@ -3138,74 +3086,78 @@
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="inlineStr">
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Z17" s="5" t="inlineStr">
         <is>
           <t>心</t>
         </is>
       </c>
-      <c r="X17" s="5" t="inlineStr">
+      <c r="AA17" s="5" t="inlineStr"/>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="Y17" s="5" t="inlineStr">
+      <c r="AD17" s="5" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="Z17" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AA17" s="5" t="inlineStr"/>
-      <c r="AB17" s="5" t="inlineStr"/>
-      <c r="AC17" s="5" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="AD17" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>心夜(希)</t>
+          <t>病CT夜(希)</t>
         </is>
       </c>
       <c r="AF17" s="7" t="inlineStr">
@@ -3228,28 +3180,28 @@
         <v>0</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="AN17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="AS17" s="5" t="n">
         <v>0</v>
@@ -3275,145 +3227,133 @@
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>夜</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>心夜</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="X18" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr"/>
+      <c r="AB18" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
+      <c r="AC18" s="5" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>CT夜</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="X18" s="5" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="Y18" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Z18" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="AA18" s="5" t="inlineStr"/>
-      <c r="AB18" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="AC18" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
         </is>
       </c>
       <c r="AE18" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ア</t>
         </is>
       </c>
       <c r="AF18" s="5" t="inlineStr">
         <is>
-          <t>ア</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AG18" s="5" t="inlineStr">
         <is>
-          <t>心</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="5" t="n">
         <v>0</v>
@@ -3422,13 +3362,13 @@
         <v>0</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN18" s="5" t="n">
         <v>1</v>
@@ -3449,10 +3389,10 @@
         <v>0</v>
       </c>
       <c r="AT18" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU18" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV18" s="5" t="n">
         <v>2</v>
@@ -3471,84 +3411,84 @@
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>MG</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="inlineStr"/>
       <c r="U19" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="W19" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="Y19" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="AA19" s="5" t="inlineStr"/>
@@ -3564,22 +3504,22 @@
       </c>
       <c r="AD19" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="AE19" s="5" t="inlineStr">
+      <c r="AF19" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
       <c r="AG19" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AH19" s="5" t="n">
@@ -3592,7 +3532,7 @@
         <v>2</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL19" s="5" t="n">
         <v>0</v>
@@ -3601,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AN19" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AO19" s="5" t="n">
         <v>0</v>
@@ -3625,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AV19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -3637,131 +3577,139 @@
           <t>白倉　知明</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
           <t>ポ</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="X20" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr"/>
+      <c r="AB20" s="6" t="inlineStr">
+        <is>
+          <t>入夜</t>
+        </is>
+      </c>
+      <c r="AC20" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AD20" s="5" t="inlineStr">
+        <is>
+          <t>ク/17休</t>
+        </is>
+      </c>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
+      <c r="AF20" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AG20" s="5" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="AB20" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC20" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AD20" s="5" t="inlineStr">
-        <is>
-          <t>病CT/17休</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="AG20" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
       <c r="AH20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI20" s="5" t="n">
         <v>0</v>
@@ -3776,28 +3724,28 @@
         <v>0</v>
       </c>
       <c r="AM20" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN20" s="5" t="n">
         <v>3</v>
       </c>
       <c r="AO20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AR20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AU20" s="5" t="n">
         <v>0</v>
@@ -3816,126 +3764,102 @@
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>夜</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>入</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>病院MR夜</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>入夜</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
           <t>心</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr">
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="X21" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
       <c r="Y21" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Z21" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Z21" s="5" t="inlineStr"/>
       <c r="AA21" s="5" t="inlineStr"/>
       <c r="AB21" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AC21" s="6" t="inlineStr">
         <is>
-          <t>入夜(希)</t>
+          <t>心夜(希)</t>
         </is>
       </c>
       <c r="AD21" s="7" t="inlineStr">
@@ -3950,16 +3874,16 @@
       </c>
       <c r="AF21" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="AG21" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AH21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI21" s="5" t="n">
         <v>0</v>
@@ -3968,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL21" s="5" t="n">
         <v>0</v>
@@ -3977,16 +3901,16 @@
         <v>2</v>
       </c>
       <c r="AN21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AQ21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR21" s="5" t="n">
         <v>0</v>
@@ -4019,17 +3943,13 @@
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>入夜</t>
+          <t>心夜</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -4044,19 +3964,19 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>入</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>入</t>
         </is>
       </c>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病院MR</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
@@ -4077,22 +3997,22 @@
       <c r="T22" s="5" t="inlineStr"/>
       <c r="U22" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>入</t>
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="W22" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
       <c r="X22" s="6" t="inlineStr">
         <is>
-          <t>CT夜</t>
+          <t>クMR夜</t>
         </is>
       </c>
       <c r="Y22" s="7" t="inlineStr">
@@ -4108,32 +4028,32 @@
       <c r="AA22" s="5" t="inlineStr"/>
       <c r="AB22" s="5" t="inlineStr">
         <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="AD22" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="AE22" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AF22" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="AG22" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
-        </is>
-      </c>
-      <c r="AC22" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="AD22" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="AE22" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AF22" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AG22" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
         </is>
       </c>
       <c r="AH22" s="5" t="n">
@@ -4152,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="AM22" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN22" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP22" s="5" t="n">
         <v>2</v>
@@ -4191,120 +4111,108 @@
           <t>清水　万慈</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr"/>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>心夜</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>クMR夜</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr"/>
       <c r="U23" s="5" t="inlineStr">
         <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
       <c r="W23" s="5" t="inlineStr">
         <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="X23" s="5" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="X23" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
       <c r="Y23" s="5" t="inlineStr">
         <is>
-          <t>ア</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="Z23" s="5" t="inlineStr"/>
       <c r="AA23" s="5" t="inlineStr"/>
       <c r="AB23" s="5" t="inlineStr">
         <is>
-          <t>ア</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AC23" s="5" t="inlineStr">
         <is>
-          <t>病CT/17業</t>
+          <t>ク/17業</t>
         </is>
       </c>
       <c r="AD23" s="6" t="inlineStr">
         <is>
-          <t>ア夜(希)</t>
+          <t>CT夜(希)</t>
         </is>
       </c>
       <c r="AE23" s="7" t="inlineStr">
@@ -4319,32 +4227,32 @@
       </c>
       <c r="AG23" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AH23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AI23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK23" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="AL23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN23" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO23" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP23" s="5" t="n">
         <v>0</v>
@@ -4362,10 +4270,10 @@
         <v>0</v>
       </c>
       <c r="AU23" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4383,30 +4291,34 @@
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr">
@@ -4414,102 +4326,114 @@
           <t>クMR</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>病院MR夜</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="inlineStr"/>
-      <c r="W24" s="5" t="inlineStr">
+      <c r="X24" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="Y24" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Z24" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AA24" s="5" t="inlineStr"/>
+      <c r="AB24" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="AD24" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="AE24" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="AF24" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="X24" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Y24" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="Z24" s="5" t="inlineStr"/>
-      <c r="AA24" s="5" t="inlineStr"/>
-      <c r="AB24" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="AC24" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AE24" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
       <c r="AG24" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AH24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AI24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="AN24" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO24" s="5" t="n">
         <v>2</v>
       </c>
       <c r="AP24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ24" s="5" t="n">
         <v>0</v>
@@ -4548,69 +4472,77 @@
           <t>病CT</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>心夜</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="P25" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
           <t>心</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>入</t>
         </is>
       </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="W25" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="X25" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="Y25" s="5" t="inlineStr">
@@ -4620,18 +4552,18 @@
       </c>
       <c r="Z25" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AA25" s="5" t="inlineStr"/>
       <c r="AB25" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="AC25" s="6" t="inlineStr">
         <is>
-          <t>病CT夜(希)</t>
+          <t>夜(希)</t>
         </is>
       </c>
       <c r="AD25" s="7" t="inlineStr">
@@ -4655,31 +4587,31 @@
         </is>
       </c>
       <c r="AH25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="AI25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="AP25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ25" s="5" t="n">
         <v>0</v>
@@ -4713,65 +4645,69 @@
       <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="P26" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr"/>
       <c r="U26" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="V26" s="5" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>病CT夜</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -4786,23 +4722,23 @@
       </c>
       <c r="Z26" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AA26" s="5" t="inlineStr"/>
       <c r="AB26" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AC26" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AD26" s="6" t="inlineStr">
         <is>
-          <t>CT夜(希)</t>
+          <t>夜(希)</t>
         </is>
       </c>
       <c r="AE26" s="7" t="inlineStr">
@@ -4817,7 +4753,7 @@
       </c>
       <c r="AG26" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AH26" s="5" t="n">
@@ -4830,19 +4766,19 @@
         <v>0</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM26" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AO26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AP26" s="5" t="n">
         <v>1</v>
@@ -4876,88 +4812,112 @@
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr"/>
       <c r="U27" s="5" t="inlineStr">
         <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="X27" s="7" t="inlineStr">
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="X27" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Y27" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="AA27" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="AB27" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="Y27" s="8" t="inlineStr">
+      <c r="AC27" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="Z27" s="5" t="inlineStr"/>
-      <c r="AA27" s="5" t="inlineStr"/>
-      <c r="AB27" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AC27" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
       <c r="AD27" s="5" t="inlineStr">
         <is>
           <t>病CT</t>
@@ -4965,21 +4925,21 @@
       </c>
       <c r="AE27" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>心</t>
         </is>
       </c>
       <c r="AF27" s="5" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AG27" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="AH27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="5" t="n">
         <v>0</v>
@@ -4988,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL27" s="5" t="n">
         <v>0</v>
@@ -4997,25 +4957,25 @@
         <v>5</v>
       </c>
       <c r="AN27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO27" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AQ27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AU27" s="5" t="n">
         <v>0</v>
@@ -5039,88 +4999,92 @@
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>PICC</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="W28" s="6" t="inlineStr">
+        <is>
+          <t>入夜</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Z28" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="X28" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="Z28" s="5" t="inlineStr"/>
       <c r="AA28" s="5" t="inlineStr"/>
       <c r="AB28" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>PICC</t>
         </is>
       </c>
       <c r="AC28" s="9" t="inlineStr">
@@ -5149,7 +5113,7 @@
         </is>
       </c>
       <c r="AH28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" s="5" t="n">
         <v>0</v>
@@ -5158,31 +5122,31 @@
         <v>0</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM28" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN28" s="5" t="n">
         <v>2</v>
       </c>
       <c r="AO28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AQ28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AS28" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT28" s="5" t="n">
         <v>0</v>
@@ -5209,7 +5173,7 @@
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>クMR夜</t>
+          <t>CT夜</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -5229,105 +5193,97 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>CT夜</t>
-        </is>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="S29" s="8" t="inlineStr">
         <is>
           <t>休</t>
-        </is>
-      </c>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
         </is>
       </c>
       <c r="T29" s="5" t="inlineStr"/>
       <c r="U29" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>病院MR夜</t>
-        </is>
-      </c>
-      <c r="W29" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="X29" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
         </is>
       </c>
       <c r="Y29" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="Z29" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
+          <t>PICC</t>
+        </is>
+      </c>
+      <c r="Z29" s="5" t="inlineStr"/>
       <c r="AA29" s="5" t="inlineStr"/>
       <c r="AB29" s="5" t="inlineStr">
         <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AD29" s="5" t="inlineStr">
+        <is>
+          <t>業配</t>
+        </is>
+      </c>
+      <c r="AE29" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AF29" s="5" t="inlineStr">
+        <is>
           <t>PICC</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="AD29" s="5" t="inlineStr">
-        <is>
-          <t>業配</t>
-        </is>
-      </c>
-      <c r="AE29" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AF29" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
       <c r="AG29" s="6" t="inlineStr">
         <is>
-          <t>病CT夜(希)</t>
+          <t>クMR夜(希)</t>
         </is>
       </c>
       <c r="AH29" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" s="5" t="n">
         <v>0</v>
@@ -5342,13 +5298,13 @@
         <v>0</v>
       </c>
       <c r="AM29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN29" s="5" t="n">
         <v>2</v>
       </c>
       <c r="AO29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP29" s="5" t="n">
         <v>1</v>
@@ -5360,10 +5316,10 @@
         <v>0</v>
       </c>
       <c r="AS29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU29" s="5" t="n">
         <v>0</v>
@@ -5390,101 +5346,109 @@
           <t>CT</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>心夜</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="N30" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr">
         <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
       <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="inlineStr">
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>OP夜</t>
+        </is>
+      </c>
+      <c r="W30" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="W30" s="8" t="inlineStr">
+      <c r="X30" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
       <c r="Y30" s="5" t="inlineStr">
         <is>
-          <t>PICC</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="Z30" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>超遅</t>
         </is>
       </c>
       <c r="AA30" s="5" t="inlineStr"/>
       <c r="AB30" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AC30" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="AD30" s="5" t="inlineStr"/>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="AD30" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="AE30" s="5" t="inlineStr">
         <is>
           <t>HB</t>
@@ -5492,12 +5456,12 @@
       </c>
       <c r="AF30" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AG30" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>精</t>
         </is>
       </c>
       <c r="AH30" s="5" t="n">
@@ -5510,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" s="5" t="n">
         <v>0</v>
@@ -5519,19 +5483,19 @@
         <v>3</v>
       </c>
       <c r="AN30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AO30" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP30" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="AQ30" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS30" s="5" t="n">
         <v>2</v>
@@ -5559,26 +5523,26 @@
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>HB夜</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
           <t>病CT</t>
@@ -5586,52 +5550,48 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
+          <t>精</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>HB夜</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>PICC</t>
         </is>
       </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>入</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr"/>
       <c r="U31" s="5" t="inlineStr">
         <is>
-          <t>PICC</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
       <c r="X31" s="6" t="inlineStr">
         <is>
           <t>HB夜</t>
@@ -5650,7 +5610,7 @@
       <c r="AA31" s="5" t="inlineStr"/>
       <c r="AB31" s="5" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="AC31" s="9" t="inlineStr">
@@ -5679,7 +5639,7 @@
         </is>
       </c>
       <c r="AH31" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI31" s="5" t="n">
         <v>1</v>
@@ -5688,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL31" s="5" t="n">
         <v>0</v>
@@ -5700,19 +5660,19 @@
         <v>0</v>
       </c>
       <c r="AO31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AQ31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT31" s="5" t="n">
         <v>0</v>
@@ -5737,51 +5697,47 @@
       <c r="D32" s="5" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>病院MR夜</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="P32" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>精夜</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
@@ -5791,18 +5747,18 @@
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr"/>
       <c r="U32" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>クMR夜</t>
+          <t>病CT夜</t>
         </is>
       </c>
       <c r="W32" s="7" t="inlineStr">
@@ -5817,30 +5773,26 @@
       </c>
       <c r="Y32" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="Z32" s="5" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AA32" s="5" t="inlineStr"/>
       <c r="AB32" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AC32" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AD32" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr"/>
       <c r="AE32" s="6" t="inlineStr">
         <is>
           <t>ク夜(希)</t>
@@ -5857,25 +5809,25 @@
         </is>
       </c>
       <c r="AH32" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN32" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="5" t="n">
         <v>0</v>
@@ -5890,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="AS32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT32" s="5" t="n">
         <v>0</v>
@@ -5915,16 +5867,8 @@
       <c r="D33" s="5" t="inlineStr"/>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
@@ -5932,86 +5876,86 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr"/>
       <c r="U33" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>超遅</t>
         </is>
       </c>
       <c r="V33" s="5" t="inlineStr"/>
-      <c r="W33" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="X33" s="5" t="inlineStr">
+      <c r="W33" s="6" t="inlineStr">
+        <is>
+          <t>ク夜</t>
+        </is>
+      </c>
+      <c r="X33" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Y33" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Z33" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
-        </is>
-      </c>
-      <c r="Y33" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="Z33" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
         </is>
       </c>
       <c r="AA33" s="5" t="inlineStr"/>
       <c r="AB33" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="AD33" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AE33" s="5" t="inlineStr">
+        <is>
           <t>精</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="AD33" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AE33" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
       <c r="AF33" s="5" t="inlineStr">
         <is>
           <t>ク</t>
@@ -6019,11 +5963,11 @@
       </c>
       <c r="AG33" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>病院MR</t>
         </is>
       </c>
       <c r="AH33" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI33" s="5" t="n">
         <v>1</v>
@@ -6032,7 +5976,7 @@
         <v>2</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL33" s="5" t="n">
         <v>0</v>
@@ -6041,10 +5985,10 @@
         <v>1</v>
       </c>
       <c r="AN33" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP33" s="5" t="n">
         <v>1</v>
@@ -6078,142 +6022,118 @@
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>病院MR夜</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr">
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>病院MR夜</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>病院MR夜</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="inlineStr">
+      <c r="X34" s="5" t="inlineStr">
+        <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="Y34" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="Z34" s="5" t="inlineStr"/>
+      <c r="AA34" s="5" t="inlineStr"/>
+      <c r="AB34" s="5" t="inlineStr"/>
+      <c r="AC34" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="W34" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="X34" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="Y34" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="Z34" s="5" t="inlineStr">
+      <c r="AD34" s="5" t="inlineStr">
+        <is>
+          <t>PICC</t>
+        </is>
+      </c>
+      <c r="AE34" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AF34" s="5" t="inlineStr">
         <is>
           <t>心</t>
         </is>
       </c>
-      <c r="AA34" s="5" t="inlineStr"/>
-      <c r="AB34" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="AC34" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AD34" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="AE34" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="AF34" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
       <c r="AG34" s="6" t="inlineStr">
         <is>
-          <t>夜(希)</t>
+          <t>クMR夜(希)</t>
         </is>
       </c>
       <c r="AH34" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI34" s="5" t="n">
         <v>1</v>
@@ -6222,19 +6142,19 @@
         <v>0</v>
       </c>
       <c r="AK34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AL34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="AN34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34" s="5" t="n">
         <v>1</v>
@@ -6246,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="AS34" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT34" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU34" s="5" t="n">
         <v>0</v>
@@ -6273,31 +6193,35 @@
       <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>心</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr"/>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>OP夜</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>超遅</t>
+        </is>
+      </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="P35" s="5" t="inlineStr">
@@ -6307,74 +6231,62 @@
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr"/>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="X35" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Y35" s="6" t="inlineStr">
+        <is>
+          <t>CT夜</t>
+        </is>
+      </c>
+      <c r="Z35" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA35" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AB35" s="5" t="inlineStr"/>
+      <c r="AC35" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AD35" s="5" t="inlineStr">
+        <is>
           <t>心</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="inlineStr">
+      <c r="AE35" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AF35" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr">
-        <is>
-          <t>PICC</t>
-        </is>
-      </c>
-      <c r="X35" s="5" t="inlineStr"/>
-      <c r="Y35" s="6" t="inlineStr">
-        <is>
-          <t>CT夜</t>
-        </is>
-      </c>
-      <c r="Z35" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA35" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AB35" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="AC35" s="5" t="inlineStr"/>
-      <c r="AD35" s="5" t="inlineStr">
-        <is>
-          <t>心</t>
-        </is>
-      </c>
-      <c r="AE35" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AF35" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
         </is>
       </c>
       <c r="AG35" s="5" t="inlineStr">
@@ -6392,16 +6304,16 @@
         <v>0</v>
       </c>
       <c r="AK35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN35" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="AL35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN35" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="AO35" s="5" t="n">
         <v>0</v>
@@ -6410,16 +6322,16 @@
         <v>2</v>
       </c>
       <c r="AQ35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AS35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT35" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AU35" s="5" t="n">
         <v>0</v>
@@ -6441,110 +6353,118 @@
       <c r="D36" s="5" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>超遅</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr"/>
+      <c r="T36" s="5" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="V36" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="X36" s="5" t="inlineStr">
         <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="P36" s="6" t="inlineStr">
+      <c r="Y36" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="Z36" s="5" t="inlineStr"/>
+      <c r="AA36" s="5" t="inlineStr"/>
+      <c r="AB36" s="6" t="inlineStr">
         <is>
           <t>夜</t>
         </is>
       </c>
-      <c r="Q36" s="7" t="inlineStr">
+      <c r="AC36" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="AD36" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="S36" s="5" t="inlineStr">
+      <c r="AE36" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="W36" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="X36" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="Y36" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Z36" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AA36" s="5" t="inlineStr"/>
-      <c r="AB36" s="5" t="inlineStr"/>
-      <c r="AC36" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AD36" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="AE36" s="5" t="inlineStr"/>
       <c r="AF36" s="5" t="inlineStr">
         <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="AG36" s="5" t="inlineStr"/>
+      <c r="AG36" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="AH36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="AI36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ36" s="5" t="n">
         <v>0</v>
@@ -6556,10 +6476,10 @@
         <v>0</v>
       </c>
       <c r="AM36" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN36" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" s="5" t="n">
         <v>0</v>
@@ -6604,29 +6524,25 @@
           <t>病CT</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>病院MR夜</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>休</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr"/>
@@ -6637,76 +6553,80 @@
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="P37" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="R37" s="7" t="inlineStr">
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="T37" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="S37" s="8" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="V37" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="W37" s="5" t="inlineStr">
         <is>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="X37" s="5" t="inlineStr"/>
+      <c r="Y37" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Z37" s="5" t="inlineStr"/>
+      <c r="AA37" s="5" t="inlineStr"/>
+      <c r="AB37" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AC37" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AD37" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="AE37" s="5" t="inlineStr">
+        <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="X37" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="Y37" s="5" t="inlineStr"/>
-      <c r="Z37" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AA37" s="5" t="inlineStr"/>
-      <c r="AB37" s="5" t="inlineStr"/>
-      <c r="AC37" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AD37" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="AE37" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="AF37" s="6" t="inlineStr">
         <is>
-          <t>病院MR夜(希)</t>
+          <t>ク夜(希)</t>
         </is>
       </c>
       <c r="AG37" s="7" t="inlineStr">
@@ -6730,10 +6650,10 @@
         <v>0</v>
       </c>
       <c r="AM37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN37" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AN37" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AO37" s="5" t="n">
         <v>0</v>
@@ -6742,13 +6662,13 @@
         <v>1</v>
       </c>
       <c r="AQ37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AR37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AT37" s="5" t="n">
         <v>0</v>
@@ -6773,123 +6693,127 @@
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>ク夜</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>ア夜</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>出</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P38" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>超遅</t>
+        </is>
+      </c>
       <c r="T38" s="5" t="inlineStr"/>
       <c r="U38" s="5" t="inlineStr">
         <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="V38" s="6" t="inlineStr">
+        <is>
+          <t>ア夜</t>
+        </is>
+      </c>
+      <c r="W38" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Y38" s="5" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="V38" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="W38" s="7" t="inlineStr">
+      <c r="Z38" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="AA38" s="5" t="inlineStr"/>
+      <c r="AB38" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AC38" s="5" t="inlineStr">
+        <is>
+          <t>ア</t>
+        </is>
+      </c>
+      <c r="AD38" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜(希)</t>
+        </is>
+      </c>
+      <c r="AE38" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="X38" s="8" t="inlineStr">
+      <c r="AF38" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="Y38" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="Z38" s="5" t="inlineStr"/>
-      <c r="AA38" s="5" t="inlineStr"/>
-      <c r="AB38" s="5" t="inlineStr"/>
-      <c r="AC38" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="AD38" s="6" t="inlineStr">
-        <is>
-          <t>CT夜(希)</t>
-        </is>
-      </c>
-      <c r="AE38" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AF38" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="AG38" s="5" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
       <c r="AH38" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI38" s="5" t="n">
         <v>1</v>
@@ -6904,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="AM38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" s="5" t="n">
         <v>0</v>
@@ -6916,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="AQ38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" s="5" t="n">
         <v>0</v>
@@ -6928,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="AU38" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV38" s="5" t="n">
         <v>0</v>
@@ -6944,125 +6868,145 @@
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>病院MR夜</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="X39" s="6" t="inlineStr">
+        <is>
+          <t>CT夜</t>
+        </is>
+      </c>
+      <c r="Y39" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Z39" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AA39" s="5" t="inlineStr"/>
+      <c r="AB39" s="5" t="inlineStr">
         <is>
           <t>超遅</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="AC39" s="5" t="inlineStr">
+        <is>
+          <t>★連</t>
+        </is>
+      </c>
+      <c r="AD39" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="AE39" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>出</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr"/>
-      <c r="X39" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="Y39" s="5" t="inlineStr">
+      <c r="AF39" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="Z39" s="5" t="inlineStr"/>
-      <c r="AA39" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="AB39" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AC39" s="5" t="inlineStr">
-        <is>
-          <t>★連</t>
-        </is>
-      </c>
-      <c r="AD39" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="AE39" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="AF39" s="5" t="inlineStr"/>
       <c r="AG39" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
       <c r="AH39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ39" s="5" t="n">
         <v>0</v>
@@ -7074,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="AM39" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP39" s="5" t="n">
         <v>2</v>
@@ -7114,30 +7058,38 @@
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
           <t>ク</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
@@ -7145,87 +7097,87 @@
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>ク夜</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="inlineStr"/>
       <c r="U40" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="V40" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr">
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr"/>
+      <c r="X40" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="Y40" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="Z40" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="AA40" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB40" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC40" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="AD40" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="X40" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="Y40" s="5" t="inlineStr"/>
-      <c r="Z40" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="AA40" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AB40" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AC40" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AD40" s="5" t="inlineStr">
+      <c r="AE40" s="5" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="AF40" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="AE40" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AF40" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AG40" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
+      <c r="AG40" s="5" t="inlineStr"/>
       <c r="AH40" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI40" s="5" t="n">
         <v>1</v>
@@ -7234,16 +7186,16 @@
         <v>0</v>
       </c>
       <c r="AK40" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM40" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO40" s="5" t="n">
         <v>0</v>
@@ -7258,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="AS40" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT40" s="5" t="n">
         <v>0</v>
@@ -7307,40 +7259,64 @@
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>超遅</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr"/>
       <c r="U41" s="5" t="inlineStr"/>
       <c r="V41" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="inlineStr"/>
-      <c r="X41" s="5" t="inlineStr"/>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="X41" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
       <c r="Y41" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="Z41" s="6" t="inlineStr">
         <is>
-          <t>精夜</t>
+          <t>夜</t>
         </is>
       </c>
       <c r="AA41" s="7" t="inlineStr">
@@ -7355,18 +7331,22 @@
       </c>
       <c r="AC41" s="5" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AD41" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AE41" s="5" t="inlineStr"/>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AE41" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="AF41" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AG41" s="9" t="inlineStr">
@@ -7375,7 +7355,7 @@
         </is>
       </c>
       <c r="AH41" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI41" s="5" t="n">
         <v>1</v>
@@ -7384,19 +7364,19 @@
         <v>0</v>
       </c>
       <c r="AK41" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO41" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP41" s="5" t="n">
         <v>2</v>
@@ -7408,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="AS41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT41" s="5" t="n">
         <v>0</v>
@@ -7431,73 +7411,61 @@
       </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
           <t>ク</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>CT夜</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>ク</t>
         </is>
       </c>
-      <c r="R42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="V42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="W42" s="5" t="inlineStr"/>
-      <c r="X42" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="X42" s="5" t="inlineStr"/>
       <c r="Y42" s="5" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>入</t>
         </is>
       </c>
       <c r="Z42" s="5" t="inlineStr">
@@ -7509,17 +7477,13 @@
       <c r="AB42" s="5" t="inlineStr"/>
       <c r="AC42" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AD42" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AD42" s="5" t="inlineStr"/>
       <c r="AE42" s="6" t="inlineStr">
         <is>
-          <t>夜(希)</t>
+          <t>ク夜(希)</t>
         </is>
       </c>
       <c r="AF42" s="7" t="inlineStr">
@@ -7533,7 +7497,7 @@
         </is>
       </c>
       <c r="AH42" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI42" s="5" t="n">
         <v>1</v>
@@ -7542,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL42" s="5" t="n">
         <v>0</v>
@@ -7551,7 +7515,7 @@
         <v>2</v>
       </c>
       <c r="AN42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO42" s="5" t="n">
         <v>1</v>
@@ -7566,7 +7530,7 @@
         <v>0</v>
       </c>
       <c r="AS42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT42" s="5" t="n">
         <v>0</v>
@@ -7600,14 +7564,10 @@
           <t>ク</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
+      <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -7615,104 +7575,112 @@
           <t>MG</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="N43" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="X43" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Y43" s="5" t="inlineStr">
+        <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="W43" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="X43" s="5" t="inlineStr">
+      <c r="Z43" s="6" t="inlineStr">
+        <is>
+          <t>ク夜</t>
+        </is>
+      </c>
+      <c r="AA43" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AB43" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AC43" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AD43" s="5" t="inlineStr">
+        <is>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="AE43" s="5" t="inlineStr"/>
+      <c r="AF43" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="AG43" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="Y43" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="Z43" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="AA43" s="5" t="inlineStr"/>
-      <c r="AB43" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AC43" s="5" t="inlineStr"/>
-      <c r="AD43" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AE43" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AF43" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AG43" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="AH43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AJ43" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK43" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL43" s="5" t="n">
         <v>0</v>
@@ -7721,13 +7689,13 @@
         <v>2</v>
       </c>
       <c r="AN43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="AO43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP43" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="AQ43" s="5" t="n">
         <v>0</v>
@@ -7758,12 +7726,12 @@
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
+      <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr">
         <is>
@@ -7771,38 +7739,46 @@
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="S44" s="5" t="inlineStr"/>
@@ -7824,47 +7800,51 @@
       </c>
       <c r="X44" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="Y44" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Z44" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AA44" s="5" t="inlineStr"/>
-      <c r="AB44" s="5" t="inlineStr"/>
-      <c r="AC44" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="Z44" s="5" t="inlineStr"/>
+      <c r="AA44" s="6" t="inlineStr">
+        <is>
+          <t>出夜</t>
+        </is>
+      </c>
+      <c r="AB44" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AC44" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
         </is>
       </c>
       <c r="AD44" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AE44" s="5" t="inlineStr"/>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="AE44" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="AF44" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AG44" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="AG44" s="5" t="inlineStr"/>
       <c r="AH44" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ44" s="5" t="n">
         <v>2</v>
@@ -7876,13 +7856,13 @@
         <v>0</v>
       </c>
       <c r="AM44" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AO44" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP44" s="5" t="n">
         <v>1</v>
@@ -7925,101 +7905,97 @@
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
       <c r="N45" s="5" t="inlineStr"/>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr"/>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
+      <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="5" t="inlineStr"/>
       <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
+      <c r="U45" s="5" t="inlineStr"/>
       <c r="V45" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="W45" s="5" t="inlineStr">
         <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="Y45" s="7" t="inlineStr">
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="X45" s="5" t="inlineStr">
+        <is>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="Y45" s="5" t="inlineStr"/>
+      <c r="Z45" s="5" t="inlineStr"/>
+      <c r="AA45" s="6" t="inlineStr">
+        <is>
+          <t>出夜</t>
+        </is>
+      </c>
+      <c r="AB45" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="Z45" s="8" t="inlineStr">
+      <c r="AC45" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="AA45" s="5" t="inlineStr"/>
-      <c r="AB45" s="5" t="inlineStr">
+      <c r="AD45" s="5" t="inlineStr">
         <is>
           <t>入</t>
         </is>
       </c>
-      <c r="AC45" s="5" t="inlineStr"/>
-      <c r="AD45" s="5" t="inlineStr">
+      <c r="AE45" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AF45" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="AE45" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="AF45" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AG45" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="AG45" s="5" t="inlineStr"/>
       <c r="AH45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI45" s="5" t="n">
         <v>1</v>
@@ -8034,28 +8010,28 @@
         <v>0</v>
       </c>
       <c r="AM45" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="AQ45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AR45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT45" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AU45" s="5" t="n">
         <v>0</v>
@@ -8073,98 +8049,130 @@
           <t>大浦　駿介</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
+          <t>精</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
       <c r="P46" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="inlineStr"/>
+          <t>超遅</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr"/>
       <c r="U46" s="5" t="inlineStr">
         <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="X46" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="Y46" s="6" t="inlineStr">
+        <is>
+          <t>病院MR夜</t>
+        </is>
+      </c>
+      <c r="Z46" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA46" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AB46" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AC46" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="V46" s="5" t="inlineStr"/>
-      <c r="W46" s="5" t="inlineStr">
-        <is>
-          <t>超遅</t>
-        </is>
-      </c>
-      <c r="X46" s="5" t="inlineStr"/>
-      <c r="Y46" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Z46" s="5" t="inlineStr"/>
-      <c r="AA46" s="5" t="inlineStr">
-        <is>
-          <t>出</t>
-        </is>
-      </c>
-      <c r="AB46" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AC46" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="AD46" s="5" t="inlineStr">
         <is>
-          <t>クMR</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AE46" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>ポ</t>
         </is>
       </c>
       <c r="AF46" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AG46" s="5" t="inlineStr">
@@ -8173,7 +8181,7 @@
         </is>
       </c>
       <c r="AH46" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI46" s="5" t="n">
         <v>1</v>
@@ -8188,19 +8196,19 @@
         <v>0</v>
       </c>
       <c r="AM46" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO46" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="AQ46" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR46" s="5" t="n">
         <v>0</v>
@@ -8240,116 +8248,124 @@
           <t>MG</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>病CT夜</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="P47" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
           <t>超遅</t>
         </is>
       </c>
-      <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr"/>
       <c r="U47" s="5" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="X47" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Y47" s="6" t="inlineStr">
+        <is>
+          <t>病院MR夜</t>
+        </is>
+      </c>
+      <c r="Z47" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="AA47" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="AB47" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AC47" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AD47" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="AE47" s="5" t="inlineStr">
+        <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="X47" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Y47" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="Z47" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AA47" s="5" t="inlineStr">
-        <is>
-          <t>出</t>
-        </is>
-      </c>
-      <c r="AB47" s="6" t="inlineStr">
-        <is>
-          <t>ク夜</t>
-        </is>
-      </c>
-      <c r="AC47" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AD47" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="AE47" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
       <c r="AF47" s="5" t="inlineStr">
         <is>
           <t>ク</t>
         </is>
       </c>
-      <c r="AG47" s="5" t="inlineStr"/>
+      <c r="AG47" s="5" t="inlineStr">
+        <is>
+          <t>病院MR</t>
+        </is>
+      </c>
       <c r="AH47" s="5" t="n">
         <v>2</v>
       </c>
@@ -8360,25 +8376,25 @@
         <v>2</v>
       </c>
       <c r="AK47" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP47" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AQ47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR47" s="5" t="n">
         <v>0</v>
@@ -8405,21 +8421,13 @@
           <t>髙谷　ひな</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>出夜</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
@@ -8429,48 +8437,52 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>休</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>CT夜</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N48" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="S48" s="5" t="inlineStr"/>
@@ -8481,67 +8493,63 @@
       </c>
       <c r="U48" s="5" t="inlineStr">
         <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="X48" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Y48" s="5" t="inlineStr">
+        <is>
           <t>ポ</t>
         </is>
       </c>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="X48" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Y48" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="Z48" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="AA48" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
+      <c r="Z48" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="AA48" s="5" t="inlineStr"/>
       <c r="AB48" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AC48" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AD48" s="5" t="inlineStr">
         <is>
-          <t>MG/17休</t>
+          <t>ク/17休</t>
         </is>
       </c>
       <c r="AE48" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AF48" s="5" t="inlineStr">
-        <is>
           <t>超遅</t>
         </is>
       </c>
-      <c r="AG48" s="5" t="inlineStr"/>
+      <c r="AF48" s="5" t="inlineStr"/>
+      <c r="AG48" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="AH48" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>2</v>
@@ -8550,19 +8558,19 @@
         <v>2</v>
       </c>
       <c r="AK48" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AL48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AM48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO48" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AN48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO48" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="AP48" s="5" t="n">
         <v>1</v>
@@ -8574,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="AS48" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT48" s="5" t="n">
         <v>0</v>
@@ -8601,19 +8609,11 @@
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
           <t>精</t>
@@ -8623,20 +8623,28 @@
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr"/>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="V49" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="W49" s="5" t="inlineStr">
@@ -8644,36 +8652,40 @@
           <t>ク</t>
         </is>
       </c>
-      <c r="X49" s="5" t="inlineStr"/>
+      <c r="X49" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
       <c r="Y49" s="5" t="inlineStr"/>
       <c r="Z49" s="5" t="inlineStr"/>
       <c r="AA49" s="5" t="inlineStr"/>
-      <c r="AB49" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="AB49" s="5" t="inlineStr"/>
       <c r="AC49" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="AD49" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AE49" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AF49" s="5" t="inlineStr">
         <is>
-          <t>PICC</t>
-        </is>
-      </c>
-      <c r="AG49" s="5" t="inlineStr"/>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AG49" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
       <c r="AH49" s="5" t="n">
         <v>0</v>
       </c>
@@ -8684,25 +8696,25 @@
         <v>0</v>
       </c>
       <c r="AK49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AL49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" s="5" t="n">
+      <c r="AN49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AN49" s="5" t="n">
+      <c r="AQ49" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="AO49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ49" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="AR49" s="5" t="n">
         <v>0</v>
@@ -8735,25 +8747,29 @@
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr">
         <is>
+          <t>PICC</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>PICC</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
       <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
+      <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>ク</t>
+        </is>
+      </c>
       <c r="P50" s="5" t="inlineStr">
         <is>
           <t>ポ</t>
@@ -8762,58 +8778,62 @@
       <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>PICC</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="S50" s="5" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr"/>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
       <c r="V50" s="5" t="inlineStr">
         <is>
-          <t>精</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr"/>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="X50" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Y50" s="5" t="inlineStr">
-        <is>
-          <t>入</t>
-        </is>
-      </c>
+          <t>ク</t>
+        </is>
+      </c>
+      <c r="Y50" s="5" t="inlineStr"/>
       <c r="Z50" s="5" t="inlineStr"/>
       <c r="AA50" s="5" t="inlineStr"/>
       <c r="AB50" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>精</t>
         </is>
       </c>
       <c r="AC50" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="AD50" s="5" t="inlineStr">
         <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AE50" s="5" t="inlineStr">
+        <is>
           <t>入</t>
         </is>
       </c>
-      <c r="AE50" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
       <c r="AF50" s="5" t="inlineStr">
         <is>
-          <t>ク</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AG50" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AH50" s="5" t="n">
@@ -8826,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL50" s="5" t="n">
         <v>0</v>
@@ -8835,22 +8855,22 @@
         <v>3</v>
       </c>
       <c r="AN50" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO50" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP50" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AQ50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AS50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT50" s="5" t="n">
         <v>0</v>
@@ -8881,10 +8901,14 @@
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -8892,49 +8916,41 @@
           <t>PICC</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>ポ</t>
+        </is>
+      </c>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="inlineStr"/>
       <c r="O51" s="5" t="inlineStr"/>
       <c r="P51" s="5" t="inlineStr">
         <is>
-          <t>PICC</t>
-        </is>
-      </c>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>ク</t>
         </is>
       </c>
       <c r="S51" s="5" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="X51" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Y51" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="Z51" s="5" t="inlineStr"/>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>PICC</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr"/>
+      <c r="W51" s="5" t="inlineStr"/>
+      <c r="X51" s="5" t="inlineStr"/>
+      <c r="Y51" s="5" t="inlineStr"/>
+      <c r="Z51" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
       <c r="AA51" s="5" t="inlineStr"/>
       <c r="AB51" s="5" t="inlineStr">
         <is>
@@ -8943,22 +8959,22 @@
       </c>
       <c r="AC51" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AD51" s="5" t="inlineStr">
         <is>
-          <t>PICC</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AE51" s="5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="AF51" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>入</t>
         </is>
       </c>
       <c r="AG51" s="5" t="inlineStr"/>
@@ -8984,19 +9000,19 @@
         <v>1</v>
       </c>
       <c r="AO51" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP51" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AQ51" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AS51" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT51" s="5" t="n">
         <v>0</v>
@@ -9026,80 +9042,84 @@
           <t>入</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>ポ</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>入</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="S52" s="5" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="V52" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr"/>
+          <t>ポ</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr">
+        <is>
+          <t>PICC</t>
+        </is>
+      </c>
       <c r="X52" s="5" t="inlineStr">
         <is>
-          <t>精</t>
+          <t>病CT</t>
         </is>
       </c>
       <c r="Y52" s="5" t="inlineStr"/>
-      <c r="Z52" s="5" t="inlineStr"/>
+      <c r="Z52" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
       <c r="AA52" s="5" t="inlineStr"/>
       <c r="AB52" s="5" t="inlineStr"/>
-      <c r="AC52" s="5" t="inlineStr"/>
-      <c r="AD52" s="5" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
+      <c r="AC52" s="5" t="inlineStr">
+        <is>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AD52" s="5" t="inlineStr"/>
       <c r="AE52" s="5" t="inlineStr">
         <is>
-          <t>病CT</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="AF52" s="5" t="inlineStr">
         <is>
-          <t>入</t>
-        </is>
-      </c>
-      <c r="AG52" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
+          <t>病CT</t>
+        </is>
+      </c>
+      <c r="AG52" s="5" t="inlineStr"/>
       <c r="AH52" s="5" t="n">
         <v>0</v>
       </c>
@@ -9116,25 +9136,25 @@
         <v>0</v>
       </c>
       <c r="AM52" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO52" s="5" t="n">
         <v>3</v>
       </c>
       <c r="AP52" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ52" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AS52" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT52" s="5" t="n">
         <v>0</v>
@@ -9164,29 +9184,21 @@
           <t>クMR</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr"/>
@@ -9227,7 +9239,11 @@
           <t>病院MR</t>
         </is>
       </c>
-      <c r="W53" s="5" t="inlineStr"/>
+      <c r="W53" s="5" t="inlineStr">
+        <is>
+          <t>クMR</t>
+        </is>
+      </c>
       <c r="X53" s="5" t="inlineStr">
         <is>
           <t>病院MR</t>
@@ -9246,30 +9262,26 @@
       <c r="AA53" s="5" t="inlineStr"/>
       <c r="AB53" s="5" t="inlineStr">
         <is>
-          <t>病院MR</t>
+          <t>クMR</t>
         </is>
       </c>
       <c r="AC53" s="5" t="inlineStr"/>
       <c r="AD53" s="5" t="inlineStr">
         <is>
+          <t>クMR</t>
+        </is>
+      </c>
+      <c r="AE53" s="5" t="inlineStr">
+        <is>
           <t>病院MR</t>
         </is>
       </c>
-      <c r="AE53" s="5" t="inlineStr">
+      <c r="AF53" s="5" t="inlineStr">
         <is>
           <t>クMR</t>
         </is>
       </c>
-      <c r="AF53" s="5" t="inlineStr">
-        <is>
-          <t>病院MR</t>
-        </is>
-      </c>
-      <c r="AG53" s="5" t="inlineStr">
-        <is>
-          <t>クMR</t>
-        </is>
-      </c>
+      <c r="AG53" s="5" t="inlineStr"/>
       <c r="AH53" s="5" t="n">
         <v>0</v>
       </c>
@@ -9501,96 +9513,56 @@
       <c r="D56" s="5" t="inlineStr"/>
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>PICC</t>
-        </is>
-      </c>
+      <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>PICC</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="6" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>夜</t>
         </is>
       </c>
-      <c r="O56" s="7" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="P56" s="8" t="inlineStr">
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="Q56" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
-      <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr"/>
-      <c r="T56" s="5" t="inlineStr"/>
       <c r="U56" s="5" t="inlineStr"/>
-      <c r="V56" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="W56" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="V56" s="5" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
       <c r="X56" s="5" t="inlineStr"/>
-      <c r="Y56" s="6" t="inlineStr">
-        <is>
-          <t>病CT夜</t>
-        </is>
-      </c>
-      <c r="Z56" s="7" t="inlineStr">
+      <c r="Y56" s="5" t="inlineStr"/>
+      <c r="Z56" s="5" t="inlineStr"/>
+      <c r="AA56" s="5" t="inlineStr"/>
+      <c r="AB56" s="6" t="inlineStr">
+        <is>
+          <t>夜</t>
+        </is>
+      </c>
+      <c r="AC56" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="AA56" s="8" t="inlineStr">
+      <c r="AD56" s="8" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="AB56" s="5" t="inlineStr">
-        <is>
-          <t>ポ</t>
-        </is>
-      </c>
-      <c r="AC56" s="5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AD56" s="5" t="inlineStr"/>
       <c r="AE56" s="5" t="inlineStr"/>
-      <c r="AF56" s="5" t="inlineStr">
-        <is>
-          <t>病CT</t>
-        </is>
-      </c>
+      <c r="AF56" s="5" t="inlineStr"/>
       <c r="AG56" s="5" t="inlineStr"/>
       <c r="AH56" s="5" t="n">
         <v>2</v>
@@ -9608,16 +9580,16 @@
         <v>0</v>
       </c>
       <c r="AM56" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN56" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AP56" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ56" s="5" t="n">
         <v>0</v>
@@ -9992,125 +9964,37 @@
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="P61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="Q61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="R61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>夜</t>
-        </is>
-      </c>
-      <c r="T61" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>休</t>
-        </is>
-      </c>
-      <c r="V61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="W61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="X61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
-      <c r="Y61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
+      <c r="O61" s="5" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr"/>
+      <c r="S61" s="5" t="inlineStr"/>
+      <c r="T61" s="5" t="inlineStr"/>
+      <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr"/>
+      <c r="W61" s="5" t="inlineStr"/>
+      <c r="X61" s="5" t="inlineStr"/>
+      <c r="Y61" s="5" t="inlineStr"/>
       <c r="Z61" s="5" t="inlineStr"/>
       <c r="AA61" s="5" t="inlineStr"/>
-      <c r="AB61" s="5" t="inlineStr">
-        <is>
-          <t>ク</t>
-        </is>
-      </c>
-      <c r="AC61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
+      <c r="AB61" s="5" t="inlineStr"/>
+      <c r="AC61" s="5" t="inlineStr"/>
       <c r="AD61" s="5" t="inlineStr"/>
-      <c r="AE61" s="5" t="inlineStr">
-        <is>
-          <t>ア</t>
-        </is>
-      </c>
+      <c r="AE61" s="5" t="inlineStr"/>
       <c r="AF61" s="6" t="inlineStr">
         <is>
-          <t>ク夜(希)</t>
+          <t>夜(希)</t>
         </is>
       </c>
       <c r="AG61" s="7" t="inlineStr">
@@ -10119,7 +10003,7 @@
         </is>
       </c>
       <c r="AH61" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI61" s="5" t="n">
         <v>0</v>
@@ -10128,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL61" s="5" t="n">
         <v>0</v>
@@ -10158,7 +10042,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV61" s="5" t="n">
         <v>0</v>
